--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56899</v>
+        <v>56900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56900</v>
+        <v>56903</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56903</v>
+        <v>56904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56904</v>
+        <v>56910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56911</v>
+        <v>56914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56914</v>
+        <v>56916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56916</v>
+        <v>56919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56919</v>
+        <v>56924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29393-2025 artfynd.xlsx
+++ b/artfynd/A 29393-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131472981</v>
       </c>
       <c r="B2" t="n">
-        <v>56924</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
